--- a/FLORES DE ESTRADA/Noviembre/EDESUR Noviembre.xlsx
+++ b/FLORES DE ESTRADA/Noviembre/EDESUR Noviembre.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Octubre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B974069-F499-46CE-87F6-B5E44CB6B705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD886163-5964-4188-AC50-6FDF748E1B19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="69">
   <si>
     <t>EDESUR - VENCIMIENTO 6/11</t>
   </si>
@@ -233,7 +233,10 @@
     <t>7-B</t>
   </si>
   <si>
-    <t>EDESUR - VENCIMIENTO 14/11</t>
+    <t>EDESUR - VENCIMIENTO 15/12</t>
+  </si>
+  <si>
+    <t>NN</t>
   </si>
 </sst>
 </file>
@@ -385,7 +388,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFFF0000"/>
         <bgColor theme="0"/>
       </patternFill>
     </fill>
@@ -548,7 +551,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -626,9 +629,9 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -644,8 +647,9 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -950,14 +954,14 @@
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="14.85546875" customWidth="1"/>
     <col min="4" max="4" width="27" customWidth="1"/>
-    <col min="5" max="5" width="6.140625" customWidth="1"/>
+    <col min="5" max="5" width="6.42578125" customWidth="1"/>
     <col min="6" max="6" width="10.42578125" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="8.85546875" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="7.7109375" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="10.42578125" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="13.85546875" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="15.42578125" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="11.140625" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="13.7109375" customWidth="1"/>
     <col min="14" max="14" width="13.5703125" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="13.7109375" hidden="1" customWidth="1"/>
@@ -1127,7 +1131,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="50">
-        <v>1458515.68</v>
+        <v>1023447.02</v>
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
@@ -1178,7 +1182,7 @@
       </c>
       <c r="L9" s="15">
         <f>C8-J34</f>
-        <v>1215906.8199999996</v>
+        <v>733416.42740000016</v>
       </c>
       <c r="M9" s="14" t="s">
         <v>19</v>
@@ -1208,10 +1212,10 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="F10" s="18">
-        <v>19700.2</v>
+        <v>19937.5</v>
       </c>
       <c r="G10" s="51">
-        <v>19937.5</v>
+        <v>20263.599999999999</v>
       </c>
       <c r="H10" s="19">
         <v>0</v>
@@ -1222,31 +1226,31 @@
       </c>
       <c r="J10" s="20">
         <f>(G10-F10)*93.78</f>
-        <v>22253.993999999933</v>
+        <v>30581.657999999865</v>
       </c>
       <c r="K10" s="21">
         <f>G10-F10</f>
-        <v>237.29999999999927</v>
+        <v>326.09999999999854</v>
       </c>
       <c r="L10" s="19">
         <f>L9*E10/100</f>
-        <v>59579.434179999989</v>
+        <v>35937.404942600013</v>
       </c>
       <c r="M10" s="19">
         <f>J10+L10+3</f>
-        <v>81836.42817999993</v>
+        <v>66522.062942599878</v>
       </c>
       <c r="N10" s="22">
         <f>J10/C7*100</f>
-        <v>28.512484304932649</v>
+        <v>39.182137091607771</v>
       </c>
       <c r="O10" s="23">
         <f>J10/L9*100</f>
-        <v>1.8302384388303654</v>
+        <v>4.1697536157478021</v>
       </c>
       <c r="P10" s="20">
         <f>C7*O10/100</f>
-        <v>1428.5011015071002</v>
+        <v>3254.4926970911597</v>
       </c>
       <c r="Q10" s="24">
         <v>0.31</v>
@@ -1260,47 +1264,47 @@
       <c r="A11" s="18">
         <v>2</v>
       </c>
-      <c r="B11" s="36">
+      <c r="B11" s="52">
         <v>2</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="36" t="s">
+      <c r="D11" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="36">
+      <c r="E11" s="52">
         <v>3.89</v>
       </c>
-      <c r="F11" s="36">
-        <v>17213.900000000001</v>
-      </c>
-      <c r="G11" s="65">
+      <c r="F11" s="52">
+        <v>17283.900000000001</v>
+      </c>
+      <c r="G11" s="57">
         <f>F11+70</f>
-        <v>17283.900000000001</v>
-      </c>
-      <c r="H11" s="37">
-        <v>0</v>
-      </c>
-      <c r="I11" s="38">
+        <v>17353.900000000001</v>
+      </c>
+      <c r="H11" s="53">
+        <v>0</v>
+      </c>
+      <c r="I11" s="54">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J11" s="38">
+      <c r="J11" s="54">
         <f>(G11-F11)*93.78</f>
         <v>6564.6</v>
       </c>
-      <c r="K11" s="57">
+      <c r="K11" s="67">
         <f t="shared" ref="K11:K25" si="2">G11-F11</f>
         <v>70</v>
       </c>
-      <c r="L11" s="37">
+      <c r="L11" s="53">
         <f>L9*E11/100</f>
-        <v>47298.775297999986</v>
-      </c>
-      <c r="M11" s="37">
+        <v>28529.899025860006</v>
+      </c>
+      <c r="M11" s="53">
         <f t="shared" ref="M11:M24" si="3">J11+L11+1</f>
-        <v>53864.375297999984</v>
+        <v>35095.499025860008</v>
       </c>
       <c r="N11" s="22" t="e">
         <f t="shared" ref="N11:N33" si="4">J11/C9*100</f>
@@ -1308,11 +1312,11 @@
       </c>
       <c r="O11" s="23">
         <f>L11/L9*100</f>
-        <v>3.8900000000000006</v>
+        <v>3.8899999999999997</v>
       </c>
       <c r="P11" s="20">
         <f>C7*O11/100</f>
-        <v>3036.1450000000004</v>
+        <v>3036.145</v>
       </c>
       <c r="Q11" s="24">
         <v>0.19</v>
@@ -1340,11 +1344,11 @@
         <v>4</v>
       </c>
       <c r="F12" s="39">
-        <v>11671.3</v>
+        <v>11756.3</v>
       </c>
       <c r="G12" s="51">
         <f>F12+85</f>
-        <v>11756.3</v>
+        <v>11841.3</v>
       </c>
       <c r="H12" s="40">
         <v>0</v>
@@ -1363,11 +1367,11 @@
       </c>
       <c r="L12" s="40">
         <f>L9*E12/100</f>
-        <v>48636.272799999984</v>
+        <v>29336.657096000006</v>
       </c>
       <c r="M12" s="40">
         <f t="shared" si="3"/>
-        <v>56608.572799999987</v>
+        <v>37308.957096000006</v>
       </c>
       <c r="N12" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1375,11 +1379,11 @@
       </c>
       <c r="O12" s="23">
         <f>J12/L9*100</f>
-        <v>0.65558477581366004</v>
+        <v>1.0868723009462276</v>
       </c>
       <c r="P12" s="20">
         <f>C7*O12/100</f>
-        <v>511.68391752256167</v>
+        <v>848.30383088853068</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
@@ -1399,10 +1403,10 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="F13" s="39">
-        <v>29605.7</v>
+        <v>29923.5</v>
       </c>
       <c r="G13" s="51">
-        <v>29923.5</v>
+        <v>30278.400000000001</v>
       </c>
       <c r="H13" s="26">
         <v>0</v>
@@ -1413,19 +1417,19 @@
       </c>
       <c r="J13" s="41">
         <f t="shared" si="5"/>
-        <v>29803.283999999931</v>
+        <v>33282.522000000135</v>
       </c>
       <c r="K13" s="42">
         <f t="shared" si="2"/>
-        <v>317.79999999999927</v>
+        <v>354.90000000000146</v>
       </c>
       <c r="L13" s="40">
         <f>L9*E13/100</f>
-        <v>59579.434179999989</v>
+        <v>35937.404942600013</v>
       </c>
       <c r="M13" s="40">
         <f t="shared" si="3"/>
-        <v>89383.718179999923</v>
+        <v>69220.926942600141</v>
       </c>
       <c r="N13" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1433,11 +1437,11 @@
       </c>
       <c r="O13" s="23">
         <f>J13/L9*100</f>
-        <v>2.4511157853362433</v>
+        <v>4.5380115247743262</v>
       </c>
       <c r="P13" s="20">
         <f>C7*O13/100</f>
-        <v>1913.095870454938</v>
+        <v>3541.9179950863618</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
@@ -1457,10 +1461,10 @@
         <v>3.89</v>
       </c>
       <c r="F14" s="39">
-        <v>7104.9</v>
+        <v>7341.7</v>
       </c>
       <c r="G14" s="51">
-        <v>7341.7</v>
+        <v>7623.9</v>
       </c>
       <c r="H14" s="26">
         <v>0</v>
@@ -1471,19 +1475,19 @@
       </c>
       <c r="J14" s="41">
         <f t="shared" si="5"/>
-        <v>22207.104000000018</v>
+        <v>26464.715999999982</v>
       </c>
       <c r="K14" s="42">
         <f t="shared" si="2"/>
-        <v>236.80000000000018</v>
+        <v>282.19999999999982</v>
       </c>
       <c r="L14" s="40">
         <f>L9*E14/100</f>
-        <v>47298.775297999986</v>
+        <v>28529.899025860006</v>
       </c>
       <c r="M14" s="40">
         <f t="shared" si="3"/>
-        <v>69506.879298</v>
+        <v>54995.615025859988</v>
       </c>
       <c r="N14" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1491,11 +1495,11 @@
       </c>
       <c r="O14" s="23">
         <f>J14/L9*100</f>
-        <v>1.8263820577961745</v>
+        <v>3.6084160391414732</v>
       </c>
       <c r="P14" s="20">
         <f>C7*O14/100</f>
-        <v>1425.4911961099142</v>
+        <v>2816.3687185499202</v>
       </c>
       <c r="R14">
         <v>2540.8200000000002</v>
@@ -1505,47 +1509,47 @@
       <c r="A15" s="39">
         <v>6</v>
       </c>
-      <c r="B15" s="39">
+      <c r="B15" s="36">
         <v>6</v>
       </c>
-      <c r="C15" s="39" t="s">
+      <c r="C15" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="39" t="s">
+      <c r="D15" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="39">
+      <c r="E15" s="36">
         <v>4</v>
       </c>
-      <c r="F15" s="39">
-        <v>14166.7</v>
-      </c>
-      <c r="G15" s="51">
+      <c r="F15" s="36">
+        <v>14436.7</v>
+      </c>
+      <c r="G15" s="56">
         <f>F15+270</f>
-        <v>14436.7</v>
-      </c>
-      <c r="H15" s="40">
-        <v>0</v>
-      </c>
-      <c r="I15" s="41">
+        <v>14706.7</v>
+      </c>
+      <c r="H15" s="37">
+        <v>0</v>
+      </c>
+      <c r="I15" s="38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J15" s="41">
+      <c r="J15" s="38">
         <f t="shared" si="5"/>
         <v>25320.6</v>
       </c>
-      <c r="K15" s="42">
+      <c r="K15" s="55">
         <f t="shared" si="2"/>
         <v>270</v>
       </c>
-      <c r="L15" s="40">
+      <c r="L15" s="37">
         <f>L9*E15/100</f>
-        <v>48636.272799999984</v>
-      </c>
-      <c r="M15" s="40">
+        <v>29336.657096000006</v>
+      </c>
+      <c r="M15" s="37">
         <f t="shared" si="3"/>
-        <v>73957.872799999983</v>
+        <v>54658.257096000001</v>
       </c>
       <c r="N15" s="46" t="e">
         <f t="shared" si="4"/>
@@ -1553,11 +1557,11 @@
       </c>
       <c r="O15" s="47">
         <f>J15/L9*100</f>
-        <v>2.0824457584669198</v>
+        <v>3.4524178971233113</v>
       </c>
       <c r="P15" s="41">
         <f>C7*O15/100</f>
-        <v>1625.3489144834309</v>
+        <v>2694.6121687047444</v>
       </c>
       <c r="Y15" s="49"/>
     </row>
@@ -1578,10 +1582,10 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="F16" s="18">
-        <v>19618.5</v>
+        <v>19858.7</v>
       </c>
       <c r="G16" s="51">
-        <v>19858.7</v>
+        <v>20071.5</v>
       </c>
       <c r="H16" s="19">
         <v>0</v>
@@ -1592,19 +1596,19 @@
       </c>
       <c r="J16" s="20">
         <f t="shared" si="5"/>
-        <v>22525.956000000067</v>
+        <v>19956.383999999933</v>
       </c>
       <c r="K16" s="21">
         <f t="shared" si="2"/>
-        <v>240.20000000000073</v>
+        <v>212.79999999999927</v>
       </c>
       <c r="L16" s="19">
         <f>L9*E16/100</f>
-        <v>59579.434179999989</v>
+        <v>35937.404942600013</v>
       </c>
       <c r="M16" s="19">
         <f t="shared" si="3"/>
-        <v>82106.39018000006</v>
+        <v>55894.788942599946</v>
       </c>
       <c r="N16" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1612,11 +1616,11 @@
       </c>
       <c r="O16" s="23">
         <f>J16/L9*100</f>
-        <v>1.8526054488287247</v>
+        <v>2.7210167722512524</v>
       </c>
       <c r="P16" s="20">
         <f>C7*O16/100</f>
-        <v>1445.9585528108196</v>
+        <v>2123.7535907421025</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
@@ -1636,11 +1640,10 @@
         <v>3.89</v>
       </c>
       <c r="F17" s="18">
-        <v>6631.43</v>
+        <v>6646.43</v>
       </c>
       <c r="G17" s="51">
-        <f>F17+15</f>
-        <v>6646.43</v>
+        <v>6715.4</v>
       </c>
       <c r="H17" s="26">
         <v>0</v>
@@ -1651,19 +1654,19 @@
       </c>
       <c r="J17" s="20">
         <f t="shared" si="5"/>
-        <v>1406.7</v>
+        <v>6468.0065999999388</v>
       </c>
       <c r="K17" s="21">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>68.969999999999345</v>
       </c>
       <c r="L17" s="19">
         <f>L9*E17/100</f>
-        <v>47298.775297999986</v>
+        <v>28529.899025860006</v>
       </c>
       <c r="M17" s="19">
         <f t="shared" si="3"/>
-        <v>48706.475297999983</v>
+        <v>34998.905625859945</v>
       </c>
       <c r="N17" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1671,11 +1674,11 @@
       </c>
       <c r="O17" s="23">
         <f>J17/L9*100</f>
-        <v>0.11569143102594</v>
+        <v>0.88190097172071291</v>
       </c>
       <c r="P17" s="20">
         <f>C7*O17/100</f>
-        <v>90.297161915746159</v>
+        <v>688.3237084280164</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
@@ -1695,10 +1698,10 @@
         <v>4</v>
       </c>
       <c r="F18" s="39">
-        <v>21845.1</v>
+        <v>22070.9</v>
       </c>
       <c r="G18" s="51">
-        <v>22070.9</v>
+        <v>22279.9</v>
       </c>
       <c r="H18" s="45">
         <v>0</v>
@@ -1709,19 +1712,19 @@
       </c>
       <c r="J18" s="41">
         <f t="shared" si="5"/>
-        <v>21175.524000000274</v>
+        <v>19600.02</v>
       </c>
       <c r="K18" s="42">
         <f t="shared" si="2"/>
-        <v>225.80000000000291</v>
+        <v>209</v>
       </c>
       <c r="L18" s="40">
         <f>L9*E18/100</f>
-        <v>48636.272799999984</v>
+        <v>29336.657096000006</v>
       </c>
       <c r="M18" s="40">
         <f t="shared" si="3"/>
-        <v>69812.796800000258</v>
+        <v>48937.677096000007</v>
       </c>
       <c r="N18" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1729,11 +1732,11 @@
       </c>
       <c r="O18" s="23">
         <f>J18/L9*100</f>
-        <v>1.7415416750438395</v>
+        <v>2.6724271870324889</v>
       </c>
       <c r="P18" s="20">
         <f>C7*O18/100</f>
-        <v>1359.2732773717166</v>
+        <v>2085.8294194788577</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
@@ -1753,10 +1756,10 @@
         <v>12.66</v>
       </c>
       <c r="F19" s="39">
-        <v>23882.6</v>
+        <v>24065</v>
       </c>
       <c r="G19" s="51">
-        <v>24065</v>
+        <v>24404.2</v>
       </c>
       <c r="H19" s="40">
         <v>0</v>
@@ -1767,19 +1770,19 @@
       </c>
       <c r="J19" s="41">
         <f t="shared" si="5"/>
-        <v>17105.472000000136</v>
+        <v>31810.176000000069</v>
       </c>
       <c r="K19" s="42">
         <f t="shared" si="2"/>
-        <v>182.40000000000146</v>
+        <v>339.20000000000073</v>
       </c>
       <c r="L19" s="40">
         <f>L9*E19/100</f>
-        <v>153933.80341199995</v>
+        <v>92850.519708840031</v>
       </c>
       <c r="M19" s="40">
         <f>J19+L19+1</f>
-        <v>171040.27541200008</v>
+        <v>124661.6957088401</v>
       </c>
       <c r="N19" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1787,11 +1790,11 @@
       </c>
       <c r="O19" s="23">
         <f>J19/L9*100</f>
-        <v>1.4068078012754417</v>
+        <v>4.3372598174230728</v>
       </c>
       <c r="P19" s="20">
         <f>C7*O19/100</f>
-        <v>1098.0134888954824</v>
+        <v>3385.2312874987083</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
@@ -1811,11 +1814,11 @@
         <v>7.75</v>
       </c>
       <c r="F20" s="39">
-        <v>18545.099999999999</v>
+        <v>18745.099999999999</v>
       </c>
       <c r="G20" s="51">
         <f>F20+200</f>
-        <v>18745.099999999999</v>
+        <v>18945.099999999999</v>
       </c>
       <c r="H20" s="26">
         <v>0</v>
@@ -1834,11 +1837,11 @@
       </c>
       <c r="L20" s="40">
         <f>L9*E20/100</f>
-        <v>94232.778549999974</v>
+        <v>56839.77312350001</v>
       </c>
       <c r="M20" s="40">
         <f t="shared" si="3"/>
-        <v>112989.77854999997</v>
+        <v>75596.77312350001</v>
       </c>
       <c r="N20" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1846,57 +1849,57 @@
       </c>
       <c r="O20" s="23">
         <f>J20/L9*100</f>
-        <v>1.5425524136792002</v>
+        <v>2.5573465904617119</v>
       </c>
       <c r="P20" s="20">
         <f>C7*O20/100</f>
-        <v>1203.9621588766158</v>
+        <v>1996.0090138553662</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="36">
         <v>12</v>
       </c>
-      <c r="B21" s="36">
+      <c r="B21" s="52">
         <v>12</v>
       </c>
-      <c r="C21" s="36" t="s">
+      <c r="C21" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="55" t="s">
+      <c r="D21" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="E21" s="36">
+      <c r="E21" s="52">
         <v>7.51</v>
       </c>
-      <c r="F21" s="36">
-        <v>15233</v>
-      </c>
-      <c r="G21" s="65">
+      <c r="F21" s="52">
         <v>15269.3</v>
       </c>
-      <c r="H21" s="56">
-        <v>0</v>
-      </c>
-      <c r="I21" s="38">
+      <c r="G21" s="57">
+        <v>15306.9</v>
+      </c>
+      <c r="H21" s="66">
+        <v>0</v>
+      </c>
+      <c r="I21" s="54">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J21" s="38">
+      <c r="J21" s="54">
         <f t="shared" si="5"/>
-        <v>3404.2139999999317</v>
-      </c>
-      <c r="K21" s="57">
+        <v>3526.1280000000343</v>
+      </c>
+      <c r="K21" s="67">
         <f t="shared" si="2"/>
-        <v>36.299999999999272</v>
-      </c>
-      <c r="L21" s="37">
+        <v>37.600000000000364</v>
+      </c>
+      <c r="L21" s="53">
         <f>L9*E21/100</f>
-        <v>91314.602181999959</v>
-      </c>
-      <c r="M21" s="37">
+        <v>55079.573697740008</v>
+      </c>
+      <c r="M21" s="53">
         <f t="shared" si="3"/>
-        <v>94719.816181999893</v>
+        <v>58606.701697740042</v>
       </c>
       <c r="N21" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1904,62 +1907,62 @@
       </c>
       <c r="O21" s="23">
         <f>J21/L9*100</f>
-        <v>0.27997326308276921</v>
+        <v>0.48078115900680651</v>
       </c>
       <c r="P21" s="20">
         <f>C7*O21/100</f>
-        <v>218.51913183610137</v>
+        <v>375.24969460481248</v>
       </c>
       <c r="S21">
         <f>G21-F21</f>
-        <v>36.299999999999272</v>
+        <v>37.600000000000364</v>
       </c>
     </row>
     <row r="22" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="39">
         <v>13</v>
       </c>
-      <c r="B22" s="36">
+      <c r="B22" s="39">
         <v>13</v>
       </c>
-      <c r="C22" s="36" t="s">
+      <c r="C22" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="36" t="s">
+      <c r="D22" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="E22" s="36">
+      <c r="E22" s="39">
         <v>4.45</v>
       </c>
-      <c r="F22" s="36">
-        <v>11607.2</v>
-      </c>
-      <c r="G22" s="65">
-        <f>F22+193</f>
+      <c r="F22" s="39">
         <v>11800.2</v>
       </c>
-      <c r="H22" s="56">
-        <v>0</v>
-      </c>
-      <c r="I22" s="38">
+      <c r="G22" s="51">
+        <f>F22+250</f>
+        <v>12050.2</v>
+      </c>
+      <c r="H22" s="26">
+        <v>0</v>
+      </c>
+      <c r="I22" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J22" s="38">
+      <c r="J22" s="41">
         <f t="shared" si="5"/>
-        <v>18099.54</v>
-      </c>
-      <c r="K22" s="57">
+        <v>23445</v>
+      </c>
+      <c r="K22" s="42">
         <f t="shared" si="2"/>
-        <v>193</v>
-      </c>
-      <c r="L22" s="37">
+        <v>250</v>
+      </c>
+      <c r="L22" s="40">
         <f>L9*E22/100</f>
-        <v>54107.853489999987</v>
-      </c>
-      <c r="M22" s="37">
+        <v>32637.031019300008</v>
+      </c>
+      <c r="M22" s="40">
         <f t="shared" si="3"/>
-        <v>72208.393489999988</v>
+        <v>56083.031019300004</v>
       </c>
       <c r="N22" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1967,15 +1970,15 @@
       </c>
       <c r="O22" s="23">
         <f>J22/L9*100</f>
-        <v>1.4885630792004281</v>
+        <v>3.1966832380771395</v>
       </c>
       <c r="P22" s="20">
         <f>C7*O22/100</f>
-        <v>1161.823483315934</v>
+        <v>2495.011267319207</v>
       </c>
       <c r="S22">
         <f>G22-F22</f>
-        <v>193</v>
+        <v>250</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1998,7 +2001,7 @@
         <v>20525.400000000001</v>
       </c>
       <c r="G23" s="51">
-        <v>20525.400000000001</v>
+        <v>20587.3</v>
       </c>
       <c r="H23" s="40">
         <v>0</v>
@@ -2009,19 +2012,19 @@
       </c>
       <c r="J23" s="41">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5804.9819999997953</v>
       </c>
       <c r="K23" s="42">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>61.899999999997817</v>
       </c>
       <c r="L23" s="40">
         <f>L9*E23/100</f>
-        <v>75021.450793999975</v>
+        <v>45251.793570580005</v>
       </c>
       <c r="M23" s="40">
         <f>J23+L23+1</f>
-        <v>75022.450793999975</v>
+        <v>51057.775570579797</v>
       </c>
       <c r="N23" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2029,11 +2032,11 @@
       </c>
       <c r="O23" s="23">
         <f>J23/L9*100</f>
-        <v>0</v>
+        <v>0.79149876974787192</v>
       </c>
       <c r="P23" s="20">
         <f>C7*O23/100</f>
-        <v>0</v>
+        <v>617.76478978821399</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2053,10 +2056,10 @@
         <v>4.45</v>
       </c>
       <c r="F24" s="39">
-        <v>31147.8</v>
+        <v>31291.8</v>
       </c>
       <c r="G24" s="51">
-        <v>31291.8</v>
+        <v>31465.9</v>
       </c>
       <c r="H24" s="40">
         <v>0</v>
@@ -2067,19 +2070,19 @@
       </c>
       <c r="J24" s="41">
         <f t="shared" si="5"/>
-        <v>13504.32</v>
+        <v>16327.098000000206</v>
       </c>
       <c r="K24" s="42">
         <f t="shared" si="2"/>
-        <v>144</v>
+        <v>174.10000000000218</v>
       </c>
       <c r="L24" s="40">
         <f>L9*E24/100</f>
-        <v>54107.853489999987</v>
+        <v>32637.031019300008</v>
       </c>
       <c r="M24" s="40">
         <f t="shared" si="3"/>
-        <v>67613.173489999986</v>
+        <v>48965.129019300213</v>
       </c>
       <c r="N24" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2087,11 +2090,11 @@
       </c>
       <c r="O24" s="23">
         <f>J24/L9*100</f>
-        <v>1.110637737849024</v>
+        <v>2.2261702069969482</v>
       </c>
       <c r="P24" s="20">
         <f>C7*O24/100</f>
-        <v>866.85275439116322</v>
+        <v>1737.525846561118</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2111,10 +2114,10 @@
         <v>9.19</v>
       </c>
       <c r="F25" s="39">
-        <v>11917.5</v>
+        <v>12050.9</v>
       </c>
       <c r="G25" s="51">
-        <v>12050.9</v>
+        <v>12201.8</v>
       </c>
       <c r="H25" s="40">
         <v>0</v>
@@ -2125,19 +2128,19 @@
       </c>
       <c r="J25" s="41">
         <f t="shared" si="5"/>
-        <v>12510.251999999966</v>
+        <v>14151.401999999965</v>
       </c>
       <c r="K25" s="42">
         <f t="shared" si="2"/>
-        <v>133.39999999999964</v>
+        <v>150.89999999999964</v>
       </c>
       <c r="L25" s="40">
         <f>L9*E25/100</f>
-        <v>111741.83675799996</v>
+        <v>67400.969678060006</v>
       </c>
       <c r="M25" s="40">
         <f>J25+L25+1</f>
-        <v>124253.08875799993</v>
+        <v>81553.371678059979</v>
       </c>
       <c r="N25" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2145,11 +2148,11 @@
       </c>
       <c r="O25" s="23">
         <f>J25/L9*100</f>
-        <v>1.0288824599240236</v>
+        <v>1.9295180025033567</v>
       </c>
       <c r="P25" s="20">
         <f>C7*O25/100</f>
-        <v>803.04275997070044</v>
+        <v>1505.9888009538699</v>
       </c>
     </row>
     <row r="26" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2188,11 +2191,11 @@
       <c r="K26" s="40"/>
       <c r="L26" s="40">
         <f>L9*E26/100</f>
-        <v>14347.700475999995</v>
+        <v>8654.313843320002</v>
       </c>
       <c r="M26" s="40">
         <f t="shared" ref="M26:M33" si="6">J26+L26</f>
-        <v>14347.700475999995</v>
+        <v>8654.313843320002</v>
       </c>
       <c r="N26" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2226,7 +2229,7 @@
       <c r="F27" s="52">
         <v>0</v>
       </c>
-      <c r="G27" s="66">
+      <c r="G27" s="57">
         <v>0</v>
       </c>
       <c r="H27" s="53">
@@ -2243,11 +2246,11 @@
       <c r="K27" s="53"/>
       <c r="L27" s="53">
         <f>L26</f>
-        <v>14347.700475999995</v>
+        <v>8654.313843320002</v>
       </c>
       <c r="M27" s="53">
         <f t="shared" si="6"/>
-        <v>14347.700475999995</v>
+        <v>8654.313843320002</v>
       </c>
       <c r="N27" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2281,7 +2284,7 @@
       <c r="F28" s="52">
         <v>0</v>
       </c>
-      <c r="G28" s="66">
+      <c r="G28" s="57">
         <v>0</v>
       </c>
       <c r="H28" s="53">
@@ -2298,11 +2301,11 @@
       <c r="K28" s="53"/>
       <c r="L28" s="53">
         <f>L27</f>
-        <v>14347.700475999995</v>
+        <v>8654.313843320002</v>
       </c>
       <c r="M28" s="53">
         <f t="shared" si="6"/>
-        <v>14347.700475999995</v>
+        <v>8654.313843320002</v>
       </c>
       <c r="N28" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2353,11 +2356,11 @@
       <c r="K29" s="40"/>
       <c r="L29" s="40">
         <f>L28</f>
-        <v>14347.700475999995</v>
+        <v>8654.313843320002</v>
       </c>
       <c r="M29" s="40">
         <f t="shared" si="6"/>
-        <v>14347.700475999995</v>
+        <v>8654.313843320002</v>
       </c>
       <c r="N29" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2408,11 +2411,11 @@
       <c r="K30" s="19"/>
       <c r="L30" s="19">
         <f t="shared" ref="L30:L33" si="7">L29</f>
-        <v>14347.700475999995</v>
+        <v>8654.313843320002</v>
       </c>
       <c r="M30" s="19">
         <f t="shared" si="6"/>
-        <v>14347.700475999995</v>
+        <v>8654.313843320002</v>
       </c>
       <c r="N30" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2463,11 +2466,11 @@
       <c r="K31" s="19"/>
       <c r="L31" s="19">
         <f t="shared" si="7"/>
-        <v>14347.700475999995</v>
+        <v>8654.313843320002</v>
       </c>
       <c r="M31" s="19">
         <f t="shared" si="6"/>
-        <v>14347.700475999995</v>
+        <v>8654.313843320002</v>
       </c>
       <c r="N31" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2486,43 +2489,43 @@
       <c r="A32" s="36">
         <v>23</v>
       </c>
-      <c r="B32" s="39">
+      <c r="B32" s="36">
         <v>23</v>
       </c>
-      <c r="C32" s="39" t="s">
+      <c r="C32" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="D32" s="39" t="s">
-        <v>59</v>
-      </c>
-      <c r="E32" s="39">
+      <c r="D32" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="E32" s="36">
         <v>1.18</v>
       </c>
-      <c r="F32" s="39">
-        <v>0</v>
-      </c>
-      <c r="G32" s="39">
-        <v>0</v>
-      </c>
-      <c r="H32" s="40">
-        <v>0</v>
-      </c>
-      <c r="I32" s="41">
+      <c r="F32" s="36">
+        <v>0</v>
+      </c>
+      <c r="G32" s="36">
+        <v>0</v>
+      </c>
+      <c r="H32" s="37">
+        <v>0</v>
+      </c>
+      <c r="I32" s="38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J32" s="41">
+      <c r="J32" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K32" s="40"/>
-      <c r="L32" s="40">
+      <c r="K32" s="37"/>
+      <c r="L32" s="37">
         <f t="shared" si="7"/>
-        <v>14347.700475999995</v>
-      </c>
-      <c r="M32" s="40">
+        <v>8654.313843320002</v>
+      </c>
+      <c r="M32" s="37">
         <f t="shared" si="6"/>
-        <v>14347.700475999995</v>
+        <v>8654.313843320002</v>
       </c>
       <c r="N32" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2541,43 +2544,43 @@
       <c r="A33" s="36">
         <v>24</v>
       </c>
-      <c r="B33" s="36">
+      <c r="B33" s="52">
         <v>24</v>
       </c>
-      <c r="C33" s="36" t="s">
+      <c r="C33" s="52" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="55" t="s">
+      <c r="D33" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="E33" s="36">
+      <c r="E33" s="52">
         <v>1.18</v>
       </c>
-      <c r="F33" s="36">
-        <v>0</v>
-      </c>
-      <c r="G33" s="36">
-        <v>0</v>
-      </c>
-      <c r="H33" s="37">
-        <v>0</v>
-      </c>
-      <c r="I33" s="38">
+      <c r="F33" s="52">
+        <v>0</v>
+      </c>
+      <c r="G33" s="52">
+        <v>0</v>
+      </c>
+      <c r="H33" s="53">
+        <v>0</v>
+      </c>
+      <c r="I33" s="54">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J33" s="38">
+      <c r="J33" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K33" s="37"/>
-      <c r="L33" s="37">
+      <c r="K33" s="53"/>
+      <c r="L33" s="53">
         <f t="shared" si="7"/>
-        <v>14347.700475999995</v>
-      </c>
-      <c r="M33" s="37">
+        <v>8654.313843320002</v>
+      </c>
+      <c r="M33" s="53">
         <f t="shared" si="6"/>
-        <v>14347.700475999995</v>
+        <v>8654.313843320002</v>
       </c>
       <c r="N33" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2609,19 +2612,19 @@
       </c>
       <c r="J34" s="30">
         <f>SUM(J10:J33)</f>
-        <v>242608.86000000028</v>
+        <v>290030.59259999986</v>
       </c>
       <c r="K34" s="29">
         <f>SUM(K10:K33)</f>
-        <v>2587.0000000000027</v>
+        <v>3092.6699999999992</v>
       </c>
       <c r="L34" s="29">
         <f>SUM(L10:L33)</f>
-        <v>1215785.2293180004</v>
+        <v>733343.08575726021</v>
       </c>
       <c r="M34" s="29">
         <f>SUM(M10:M33)</f>
-        <v>1458412.0893180005</v>
+        <v>1023391.6783572601</v>
       </c>
       <c r="N34" s="5"/>
       <c r="O34" s="2" t="e">
@@ -2663,7 +2666,7 @@
       <c r="H37" s="5"/>
       <c r="K37" s="34">
         <f>J34+L34</f>
-        <v>1458394.0893180007</v>
+        <v>1023373.6783572601</v>
       </c>
       <c r="L37" s="34"/>
       <c r="O37" s="2"/>
